--- a/astro-site/public/dl/kit-tareas-pasteleria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/03-tareas-manager.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Diario Manager" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Semanal Manager" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mensual Manager" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diario Manager" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanal Manager" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual Manager" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Diario Manager'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal Manager'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual Manager'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Handover Turno'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,6 +98,12 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -126,7 +137,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,54 +159,104 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -557,13 +618,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B8"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -571,6 +633,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -606,8 +669,24 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -616,18 +695,18 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -644,10 +723,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -687,18 +767,16 @@
           <t xml:space="preserve">  Primera Hora (antes de producción)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -724,10 +802,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="25" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -753,10 +829,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -782,10 +856,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="25" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -811,10 +883,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="25" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -839,24 +909,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Durante la Jornada</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="23" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="24" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -882,10 +951,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="25" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -911,10 +978,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="25" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -940,10 +1005,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="25" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -969,10 +1032,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="25" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -998,10 +1059,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="25" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1026,24 +1085,23 @@
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="15" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cierre de Día</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="25" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1069,10 +1127,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="25" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1098,10 +1154,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="25" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1127,10 +1181,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="25" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1156,10 +1208,8 @@
       <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="25" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1184,6 +1234,8 @@
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="15" t="n"/>
     </row>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
@@ -1192,7 +1244,7 @@
       </c>
       <c r="D28" s="16">
         <f>COUNTIF(F5:F26,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
@@ -1203,6 +1255,7 @@
         <v>16</v>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
@@ -1210,13 +1263,17 @@
         </is>
       </c>
       <c r="B30" s="15" t="n"/>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="24" t="n"/>
       <c r="E30" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F30" s="15" t="n"/>
-    </row>
+      <c r="G30" s="24" t="n"/>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
@@ -1236,11 +1293,20 @@
     <mergeCell ref="A28:C28"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F25" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1249,18 +1315,18 @@
   <sheetPr>
     <tabColor rgb="00FF8C00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1277,10 +1343,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1320,18 +1387,16 @@
           <t xml:space="preserve">  Lunes — Planificación</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1357,10 +1422,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="25" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1386,10 +1449,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1415,10 +1476,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="25" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1443,24 +1502,23 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="15" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martes — Equipo</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="23" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="25" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -1486,10 +1544,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1515,10 +1571,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="25" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1543,24 +1597,23 @@
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="15" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Miércoles — Calidad</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="23" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="23" t="n"/>
+      <c r="F16" s="23" t="n"/>
+      <c r="G16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="25" t="n">
+        <v>8</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1586,10 +1639,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="25" t="n">
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1615,10 +1666,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="25" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1644,10 +1693,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="25" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1672,24 +1719,23 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="15" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Jueves — Proveedores y Compras</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="25" t="n">
+        <v>12</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1715,10 +1761,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="25" t="n">
+        <v>13</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1744,10 +1788,8 @@
       <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="25" t="n">
+        <v>14</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1772,24 +1814,23 @@
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="15" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Viernes — Preparación Fin de Semana</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="24" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="25" t="n">
+        <v>15</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -1815,10 +1856,8 @@
       <c r="G28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="25" t="n">
+        <v>16</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -1844,10 +1883,8 @@
       <c r="G29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="25" t="n">
+        <v>17</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -1873,10 +1910,8 @@
       <c r="G30" s="15" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A31" s="25" t="n">
+        <v>18</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -1901,6 +1936,8 @@
       <c r="F31" s="14" t="n"/>
       <c r="G31" s="15" t="n"/>
     </row>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
         <is>
@@ -1909,7 +1946,7 @@
       </c>
       <c r="D34" s="16">
         <f>COUNTIF(F5:F32,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
@@ -1920,6 +1957,7 @@
         <v>18</v>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
@@ -1927,13 +1965,17 @@
         </is>
       </c>
       <c r="B36" s="15" t="n"/>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="24" t="n"/>
       <c r="E36" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F36" s="15" t="n"/>
-    </row>
+      <c r="G36" s="24" t="n"/>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
@@ -1946,20 +1988,29 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A16:G16"/>
-    <mergeCell ref="F36:G36"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="F36:G36"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25 F28 F29 F30 F31" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1968,18 +2019,18 @@
   <sheetPr>
     <tabColor rgb="008B4513"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1996,10 +2047,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2039,18 +2091,16 @@
           <t xml:space="preserve">  Revisión Financiera</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -2076,10 +2126,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="25" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2105,10 +2153,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2134,10 +2180,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="25" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2162,24 +2206,23 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="15" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Mantenimiento</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="23" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="25" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -2205,10 +2248,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -2234,10 +2275,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="25" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2263,10 +2302,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="25" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2292,10 +2329,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="25" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2320,24 +2355,23 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="15" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Evaluación y Desarrollo</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="25" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -2363,10 +2397,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="25" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -2392,10 +2424,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="25" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -2421,10 +2451,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="25" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -2450,10 +2478,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="25" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2478,6 +2504,8 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="15" t="n"/>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
@@ -2486,7 +2514,7 @@
       </c>
       <c r="D26" s="16">
         <f>COUNTIF(F5:F24,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
@@ -2497,6 +2525,7 @@
         <v>14</v>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
@@ -2504,13 +2533,17 @@
         </is>
       </c>
       <c r="B28" s="15" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="24" t="n"/>
       <c r="E28" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-    </row>
+      <c r="G28" s="24" t="n"/>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
@@ -2521,20 +2554,29 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="F28:G28"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="F28:G28"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="B28:D28"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F19 F20 F21 F22 F23" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2543,18 +2585,18 @@
   <sheetPr>
     <tabColor rgb="00607D8B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2571,10 +2613,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2614,18 +2657,16 @@
           <t xml:space="preserve">  Traspaso de Información</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n"/>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="20" t="n"/>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -2651,10 +2692,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="25" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2680,10 +2719,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2709,10 +2746,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="25" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2738,10 +2773,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="25" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -2767,10 +2800,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -2795,6 +2826,8 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
@@ -2803,7 +2836,7 @@
       </c>
       <c r="D14" s="16">
         <f>COUNTIF(F5:F12,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
@@ -2814,6 +2847,7 @@
         <v>6</v>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
@@ -2821,13 +2855,17 @@
         </is>
       </c>
       <c r="B16" s="15" t="n"/>
+      <c r="C16" s="23" t="n"/>
+      <c r="D16" s="24" t="n"/>
       <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F16" s="15" t="n"/>
-    </row>
+      <c r="G16" s="24" t="n"/>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
@@ -2845,10 +2883,19 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pasteleria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/03-tareas-manager.xlsx
@@ -256,6 +256,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -673,14 +683,15 @@
     <row r="10">
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -697,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -752,7 +763,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -780,7 +791,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Revisar pedidos especiales del día (tartas encargo, catering)</t>
+          <t>Revisar pedidos especiales del día (tartas encargo, catering) → 11 Control de Encargos · Ficha de Encargo</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -956,7 +967,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Control de temperaturas de cámaras y vitrinas (registrar)</t>
+          <t>Control de temperaturas de cámaras y vitrinas (registrar) → 13 Registro de Temperaturas</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1010,7 +1021,7 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Gestionar pedidos de clientes (tartas personalizadas, eventos)</t>
+          <t>Gestionar pedidos de clientes (tartas personalizadas, eventos) → 11 Control de Encargos · Ficha de Encargo</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1105,7 +1116,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Revisar mermas del día (registrar producto descartado)</t>
+          <t>Revisar mermas del día (registrar producto descartado) → 10 Plan de Producción Semanal · hoja Producido vs Vendido</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -1234,48 +1245,84 @@
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="15" t="n"/>
     </row>
-    <row r="26"/>
-    <row r="27"/>
+    <row r="26">
+      <c r="A26" s="25" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="15" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="25" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="15" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D28" s="16">
-        <f>COUNTIF(F5:F26,"✓")</f>
+      <c r="D31" s="16">
+        <f>COUNTIF(F5:F29,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F28" s="16" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="F31" s="16">
+        <f>COUNTIF(B5:B29,"?*")</f>
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="24" t="n"/>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="24" t="n"/>
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="24" t="n"/>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="24" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -1283,18 +1330,23 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G29">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1317,7 +1369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1372,7 +1424,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1427,7 +1479,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Revisar pedidos especiales de la semana (tartas, eventos)</t>
+          <t>Revisar pedidos especiales de la semana (tartas, eventos) → 11 Control de Encargos · Ficha de Encargo</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1644,7 +1696,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Revisar registros de temperatura de cámaras (últimos 3 días)</t>
+          <t>Revisar registros de temperatura de cámaras (últimos 3 días) → 13 Registro de Temperaturas</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1671,7 +1723,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Verificar etiquetado de alérgenos actualizado</t>
+          <t>Verificar etiquetado de alérgenos actualizado → 12 Control de Alérgenos de Vitrina</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -1936,48 +1988,84 @@
       <c r="F31" s="14" t="n"/>
       <c r="G31" s="15" t="n"/>
     </row>
-    <row r="32"/>
-    <row r="33"/>
+    <row r="32">
+      <c r="A32" s="25" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="15" t="n"/>
+    </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="25" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="15" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="25" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="15" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D34" s="16">
-        <f>COUNTIF(F5:F32,"✓")</f>
+      <c r="D37" s="16">
+        <f>COUNTIF(F5:F35,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F34" s="16" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="F37" s="16">
+        <f>COUNTIF(B5:B35,"?*")</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="24" t="n"/>
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="24" t="n"/>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="24" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -1989,16 +2077,21 @@
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A22:G22"/>
+    <mergeCell ref="B39:D39"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G35">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25 F28 F29 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2021,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2076,7 +2169,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2131,7 +2224,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Analizar mermas del mes (objetivo: &lt;5%)</t>
+          <t>Analizar mermas del mes (objetivo: &lt;5%) → 10 Plan de Producción Semanal · hoja Producido vs Vendido</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -2504,48 +2597,84 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="15" t="n"/>
     </row>
-    <row r="24"/>
-    <row r="25"/>
+    <row r="24">
+      <c r="A24" s="25" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="15" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="15" t="n"/>
+    </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="25" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="15" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D26" s="16">
-        <f>COUNTIF(F5:F24,"✓")</f>
+      <c r="D29" s="16">
+        <f>COUNTIF(F5:F27,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F26" s="16" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="F29" s="16">
+        <f>COUNTIF(B5:B27,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="23" t="n"/>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="24" t="n"/>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="24" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -2553,18 +2682,23 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="F31:G31"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A18:G18"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="F28:G28"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="B28:D28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G27">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F19 F20 F21 F22 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2587,7 +2721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2642,7 +2776,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2697,7 +2831,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Pedidos especiales pendientes (tartas encargo, catering)</t>
+          <t>Pedidos especiales pendientes (tartas encargo, catering) → 11 Control de Encargos · Ficha de Encargo</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -2826,48 +2960,84 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
+    <row r="12">
+      <c r="A12" s="25" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="15" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="15" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="25" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="15" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D14" s="16">
-        <f>COUNTIF(F5:F12,"✓")</f>
+      <c r="D17" s="16">
+        <f>COUNTIF(F5:F15,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F14" s="16" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="F17" s="16">
+        <f>COUNTIF(B5:B15,"?*")</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="23" t="n"/>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="24" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="24" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -2875,16 +3045,21 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F19:G19"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A17:C17"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G15">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
